--- a/assets/template_sus.xlsx
+++ b/assets/template_sus.xlsx
@@ -1463,8 +1463,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023107A54E8B8B9488EB77197E8D12F37" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="8d358518067bbe07db32bef8a7675f16">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe95f226-17bd-48ac-b121-8b008b204525" xmlns:ns3="f1c2b24c-1bef-4db6-ac93-0552d2349689" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d9719c90ba3395da330de7fcde79a24" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023107A54E8B8B9488EB77197E8D12F37" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e5c38d44df2b44e63399d3149ec89ef1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe95f226-17bd-48ac-b121-8b008b204525" xmlns:ns3="f1c2b24c-1bef-4db6-ac93-0552d2349689" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="86f85a61143a6e528cde30bd9651738c" ns2:_="" ns3:_="">
     <xsd:import namespace="fe95f226-17bd-48ac-b121-8b008b204525"/>
     <xsd:import namespace="f1c2b24c-1bef-4db6-ac93-0552d2349689"/>
     <xsd:element name="properties">
@@ -1678,22 +1678,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA3E245F-0EDE-40A2-BB0A-BD0661313DEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fe95f226-17bd-48ac-b121-8b008b204525"/>
-    <ds:schemaRef ds:uri="f1c2b24c-1bef-4db6-ac93-0552d2349689"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7FBAC1-69E5-426C-B2D0-8A387E174E61}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
